--- a/demo/demo4-complete/output/post-method-triangles.xlsx
+++ b/demo/demo4-complete/output/post-method-triangles.xlsx
@@ -599,34 +599,34 @@
         <v>2015</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.2583352905404224</v>
+        <v>0.2498171604816017</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.4588835719574421</v>
+        <v>0.4437527319564006</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.5978190322744751</v>
+        <v>0.5781070515462535</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.7191644021449782</v>
+        <v>0.6954512815011442</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.8002895161588778</v>
+        <v>0.7739014444049518</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.8596552006069741</v>
+        <v>0.8313096548273277</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.9122526912326041</v>
+        <v>0.88217284014384</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.9492569469924079</v>
+        <v>0.9179569487737937</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.9801926495218027</v>
+        <v>0.9478726035309499</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1</v>
+        <v>0.9670268431347445</v>
       </c>
     </row>
     <row r="4">
@@ -634,31 +634,31 @@
         <v>2016</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.256148835089121</v>
+        <v>0.2526182445687076</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.4416643639024352</v>
+        <v>0.4355767468502014</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.5862060686421999</v>
+        <v>0.5781261818520186</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.708624272752656</v>
+        <v>0.6988570523042598</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.7985904662376105</v>
+        <v>0.7875832097384349</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.8576979404955168</v>
+        <v>0.84587598465083</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9094015543255441</v>
+        <v>0.8968669491775884</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.9483478002230028</v>
+        <v>0.9352763851124977</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.9801999607920017</v>
+        <v>0.9666895160207898</v>
       </c>
       <c r="K4" s="7" t="n"/>
     </row>
@@ -667,28 +667,28 @@
         <v>2017</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.2346667771835249</v>
+        <v>0.2232704044909342</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.4438343565278112</v>
+        <v>0.422279955851778</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.5983423722623977</v>
+        <v>0.5692844342197311</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.7191409512295325</v>
+        <v>0.6842165431088788</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.8018588880131264</v>
+        <v>0.7629173606084304</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.8607294876761786</v>
+        <v>0.8189289646247672</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.9088549277907571</v>
+        <v>0.8647172377226794</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.948794851216728</v>
+        <v>0.9027175160990236</v>
       </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -698,25 +698,25 @@
         <v>2018</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.2401776450962767</v>
+        <v>0.2393900803870952</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.4461403225726501</v>
+        <v>0.4446773871972108</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.5987819566522976</v>
+        <v>0.596818495242869</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.7287858803426835</v>
+        <v>0.7263961240450999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.8043915241006208</v>
+        <v>0.8017538499053708</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.8607095044141044</v>
+        <v>0.8578871583532881</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.9098531369550518</v>
+        <v>0.9068696443784775</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -727,22 +727,22 @@
         <v>2019</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2521663750851686</v>
+        <v>0.2466242892256292</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.4586808745519689</v>
+        <v>0.4486000349156887</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.6084389694259711</v>
+        <v>0.5950667622563611</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.7199010697170142</v>
+        <v>0.7040791603232717</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.798960729647218</v>
+        <v>0.7814012554286205</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.8594060044914064</v>
+        <v>0.8405180704300689</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
@@ -754,19 +754,19 @@
         <v>2020</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.2412185784232409</v>
+        <v>0.2358609710217281</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.4405350512051961</v>
+        <v>0.430750506969878</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.6031146527455643</v>
+        <v>0.5897191193308831</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.7224847195346856</v>
+        <v>0.7064379062827344</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.8002663232064495</v>
+        <v>0.7824919344988376</v>
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -779,16 +779,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.2546229826722554</v>
+        <v>0.2634790904514784</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.4713848006669843</v>
+        <v>0.4877801572698399</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.6195751464132588</v>
+        <v>0.6411247497380554</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.7409837824104035</v>
+        <v>0.7667561308874049</v>
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -802,13 +802,13 @@
         <v>2022</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.2427990467943571</v>
+        <v>0.2389505343215232</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.433237663337935</v>
+        <v>0.4263705830381117</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.5818896569007991</v>
+        <v>0.5726663521474966</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
@@ -823,10 +823,10 @@
         <v>2023</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.2544457809983571</v>
+        <v>0.2528384882449371</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.4496044122394346</v>
+        <v>0.4467643340472843</v>
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -842,7 +842,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.3665439273360666</v>
+        <v>0.3355129964518225</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
@@ -943,34 +943,34 @@
         <v>2015</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.2054605164880854</v>
+        <v>0.1973906077919439</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.3752037014440986</v>
+        <v>0.3604667599389223</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.5110279252223597</v>
+        <v>0.4909561918878325</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.6177140844977923</v>
+        <v>0.5934520201974385</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.7030863037730498</v>
+        <v>0.6754710598617694</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.778065179172881</v>
+        <v>0.7475049768386468</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.8493236083926482</v>
+        <v>0.8159645762517765</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.9027932241932449</v>
+        <v>0.8673340565864255</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.9584014165582122</v>
+        <v>0.9207581162391167</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1</v>
+        <v>0.9607228248323346</v>
       </c>
     </row>
     <row r="4">
@@ -978,31 +978,31 @@
         <v>2016</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.1976843477834949</v>
+        <v>0.1935225509766421</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.372083021479576</v>
+        <v>0.3642496550646801</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.5087674013349983</v>
+        <v>0.4980564544641528</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.6197431765978194</v>
+        <v>0.6066958857912736</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.711841607468003</v>
+        <v>0.6968553925138992</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.7895667186273158</v>
+        <v>0.7729441772616268</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.8566825905171651</v>
+        <v>0.8386470762760201</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.9079965461670013</v>
+        <v>0.8888807326549988</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.9584052137243626</v>
+        <v>0.938228159734648</v>
       </c>
       <c r="K4" s="7" t="n"/>
     </row>
@@ -1011,28 +1011,28 @@
         <v>2017</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.1984573735561601</v>
+        <v>0.1873257818675859</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.3711718947002414</v>
+        <v>0.3503526431700968</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.5166845632896174</v>
+        <v>0.4877034199475097</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.6225129525720597</v>
+        <v>0.5875958321612125</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7147850278411155</v>
+        <v>0.6746923120480093</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7932482447586577</v>
+        <v>0.7487544806313562</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.856077438037776</v>
+        <v>0.8080595472268783</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.9053516094127739</v>
+        <v>0.8545699011295863</v>
       </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -1042,25 +1042,25 @@
         <v>2018</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.1966140668799878</v>
+        <v>0.1952949335795867</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.3675397938922135</v>
+        <v>0.3650738768342965</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.5057054917757309</v>
+        <v>0.5023125862477441</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.6153777128064284</v>
+        <v>0.6112489887218839</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.7091941349035239</v>
+        <v>0.7044359728114319</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7861677547030782</v>
+        <v>0.7808931572066365</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.854185875472001</v>
+        <v>0.8484549272700335</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -1071,22 +1071,22 @@
         <v>2019</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2087779506261234</v>
+        <v>0.2032077675838385</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.3759034170691119</v>
+        <v>0.3658743367327264</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.5152732670546887</v>
+        <v>0.5015258075855102</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.6163990238198003</v>
+        <v>0.5999535353021426</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.7089606745372342</v>
+        <v>0.6900456468002963</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.7866880415104078</v>
+        <v>0.7656992523435058</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
@@ -1098,19 +1098,19 @@
         <v>2020</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.20669525137568</v>
+        <v>0.2002199654950042</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.3670423416699193</v>
+        <v>0.3555437509823877</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.5099169854722347</v>
+        <v>0.4939424614598577</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.6221552411359822</v>
+        <v>0.6026645512352549</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.7093030759267946</v>
+        <v>0.6870822452008833</v>
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -1123,16 +1123,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.2214664007110416</v>
+        <v>0.2303840966344883</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.3951622617007339</v>
+        <v>0.4110740969902163</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.5273751959978458</v>
+        <v>0.5486107948082183</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.6407319529488432</v>
+        <v>0.6665320413888458</v>
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
         <v>2022</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.1907557172406885</v>
+        <v>0.1878726975403905</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.3528730077706008</v>
+        <v>0.3475398002116243</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.490530976982187</v>
+        <v>0.4831172517701577</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
@@ -1167,10 +1167,10 @@
         <v>2023</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.2036084856113567</v>
+        <v>0.2026628936300336</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.3732840463381527</v>
+        <v>0.3715504525740549</v>
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -1186,7 +1186,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.3127936451136711</v>
+        <v>0.283475867352249</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
@@ -1287,34 +1287,34 @@
         <v>2015</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.3322515212981744</v>
+        <v>0.3268808621033726</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.543002028397566</v>
+        <v>0.5342247056475753</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.7042596348884381</v>
+        <v>0.6928756735182598</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.8269776876267748</v>
+        <v>0.8136100578726801</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.918052738336714</v>
+        <v>0.9032129315505887</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.9594320486815415</v>
+        <v>0.943923368589104</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.9799188640973631</v>
+        <v>0.9640790261424865</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.9904665314401623</v>
+        <v>0.9744561963679904</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1</v>
+        <v>0.9838355617641189</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1</v>
+        <v>0.9838355617641189</v>
       </c>
     </row>
     <row r="4">
@@ -1322,31 +1322,31 @@
         <v>2016</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.3309730932632005</v>
+        <v>0.3264166001596169</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.5508800323690066</v>
+        <v>0.5432960893854749</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.7028120574549869</v>
+        <v>0.6931364724660815</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.8407849484118957</v>
+        <v>0.8292098962490024</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.921505158810439</v>
+        <v>0.9088188347964884</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.9595387416548654</v>
+        <v>0.9463288108539505</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9803762897026097</v>
+        <v>0.966879489225858</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.990086991705442</v>
+        <v>0.9764565043894653</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1</v>
+        <v>0.9862330407023144</v>
       </c>
       <c r="K4" s="7" t="n"/>
     </row>
@@ -1355,28 +1355,28 @@
         <v>2017</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.3306412942635853</v>
+        <v>0.327683615819209</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.5460467679894925</v>
+        <v>0.5411622276029056</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.7079062685680333</v>
+        <v>0.7015738498789347</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.8375974658869396</v>
+        <v>0.8301049233252623</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.9194434020285414</v>
+        <v>0.9112187247780468</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.9595519826750477</v>
+        <v>0.9509685230024213</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.9797080714263378</v>
+        <v>0.9709443099273608</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.9902951079421668</v>
+        <v>0.9814366424535916</v>
       </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -1386,25 +1386,25 @@
         <v>2018</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.3402732272419509</v>
+        <v>0.3399439102564102</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.5486078666670463</v>
+        <v>0.5480769230769231</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.713831873294841</v>
+        <v>0.7131410256410257</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.8429632571155931</v>
+        <v>0.8421474358974359</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.9207629107218848</v>
+        <v>0.9198717948717948</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.9570560481000775</v>
+        <v>0.9561298076923077</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.9797141946400542</v>
+        <v>0.9787660256410257</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -1415,22 +1415,22 @@
         <v>2019</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.3136313586349914</v>
+        <v>0.3143145161290323</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.540556421200912</v>
+        <v>0.5417338709677419</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7131643145356281</v>
+        <v>0.7147177419354839</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.8380938037673983</v>
+        <v>0.8399193548387097</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.9193683829133485</v>
+        <v>0.9213709677419355</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.9589997989820421</v>
+        <v>0.9610887096774193</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
@@ -1442,19 +1442,19 @@
         <v>2020</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.3249156750805926</v>
+        <v>0.328412537917088</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.5501958783692301</v>
+        <v>0.5561172901921132</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.6990488723716691</v>
+        <v>0.706572295247725</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.8312959544087822</v>
+        <v>0.840242669362993</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.9197274374048549</v>
+        <v>0.9296258847320525</v>
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -1467,16 +1467,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.3218663613977139</v>
+        <v>0.3277900220396714</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.5406410520299009</v>
+        <v>0.5505910639150471</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.7041318505149256</v>
+        <v>0.7170907633740733</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.8461780075620828</v>
+        <v>0.8617511520737328</v>
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -1490,13 +1490,13 @@
         <v>2022</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.3479902221223782</v>
+        <v>0.3490968134767607</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.5630562721898712</v>
+        <v>0.5648467627359448</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7218773910073519</v>
+        <v>0.7241729247006292</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
@@ -1511,10 +1511,10 @@
         <v>2023</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.3465725303834443</v>
+        <v>0.3432574430823117</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.5890406846121677</v>
+        <v>0.5834063047285464</v>
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -1530,7 +1530,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.467617508811387</v>
+        <v>0.4366233103800051</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
@@ -1631,34 +1631,34 @@
         <v>2015</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.2760089231393226</v>
+        <v>0.2715482841181165</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.4554857026972217</v>
+        <v>0.4481245011971269</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.587304806327317</v>
+        <v>0.5778132482043097</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.7197323058203204</v>
+        <v>0.7081005586592178</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.8142364631920503</v>
+        <v>0.8010774142059058</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.8815656053538836</v>
+        <v>0.86731843575419</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.9316568647333198</v>
+        <v>0.9166001596169194</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.9614682620158183</v>
+        <v>0.9459297685554668</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.9902656661934699</v>
+        <v>0.9742617717478053</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1</v>
+        <v>0.9838387869114126</v>
       </c>
     </row>
     <row r="4">
@@ -1666,31 +1666,31 @@
         <v>2016</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.2613503865068321</v>
+        <v>0.2575364344180475</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.444903448658142</v>
+        <v>0.4384108604511879</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.5875318766432659</v>
+        <v>0.5789578758235177</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.7161810979082569</v>
+        <v>0.7057296865641844</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.8126173645572895</v>
+        <v>0.8007586344579757</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.8798796345730013</v>
+        <v>0.8670393292074267</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9307315314824701</v>
+        <v>0.9171491315631862</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.9601081253146334</v>
+        <v>0.9460970253543621</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.9902951079421668</v>
+        <v>0.9758434817328808</v>
       </c>
       <c r="K4" s="7" t="n"/>
     </row>
@@ -1699,28 +1699,28 @@
         <v>2017</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.2765563972097618</v>
+        <v>0.2736459175424414</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.4366894957418544</v>
+        <v>0.4320937752627324</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.5804824821788355</v>
+        <v>0.5743734842360549</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.7046673341016827</v>
+        <v>0.6972514147130153</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.8037292636782961</v>
+        <v>0.7952708164915118</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.8756257568967866</v>
+        <v>0.866410670978173</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.9293438754094656</v>
+        <v>0.9195634599838318</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.9607985911925552</v>
+        <v>0.9506871463217461</v>
       </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -1730,25 +1730,25 @@
         <v>2018</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.2815736353957355</v>
+        <v>0.2798019801980198</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.4567351538053969</v>
+        <v>0.4538613861386139</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.5968245138076631</v>
+        <v>0.593069306930693</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.715193048432622</v>
+        <v>0.7106930693069307</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.806858916997405</v>
+        <v>0.8017821782178218</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.876604686557566</v>
+        <v>0.8710891089108911</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.9310063868144915</v>
+        <v>0.9251485148514852</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -1759,22 +1759,22 @@
         <v>2019</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2796312999262086</v>
+        <v>0.2803398058252427</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.4541486696492752</v>
+        <v>0.4552993527508091</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.5905344984733135</v>
+        <v>0.5920307443365695</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.711183500894578</v>
+        <v>0.7129854368932039</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.8070167386037765</v>
+        <v>0.8090614886731392</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.8786394741548618</v>
+        <v>0.8808656957928802</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
@@ -1786,19 +1786,19 @@
         <v>2020</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.279687591290643</v>
+        <v>0.2837589376915219</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.4707772414956972</v>
+        <v>0.4776302349336057</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.6052850247801821</v>
+        <v>0.6140960163432073</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.7156297332231428</v>
+        <v>0.726046986721144</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.8090602892770365</v>
+        <v>0.8208375893769152</v>
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -1811,16 +1811,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.2975297777452989</v>
+        <v>0.3059262166405023</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.4774980782031673</v>
+        <v>0.4909733124018839</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.6168160626509339</v>
+        <v>0.6342229199372057</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.727125370884919</v>
+        <v>0.7476452119309263</v>
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -1834,13 +1834,13 @@
         <v>2022</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.3099417362478868</v>
+        <v>0.3112569610182975</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.4788748359408245</v>
+        <v>0.4809069212410501</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.6175069224414768</v>
+        <v>0.6201272871917264</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
@@ -1855,10 +1855,10 @@
         <v>2023</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.2988158529543</v>
+        <v>0.2948545861297539</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.5019562203648105</v>
+        <v>0.4953020134228188</v>
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -1874,7 +1874,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.3871337370527187</v>
+        <v>0.3636869952659426</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
@@ -1975,34 +1975,34 @@
         <v>2015</v>
       </c>
       <c r="B3" s="8" t="n">
-        <v>33381169.87</v>
+        <v>34915843.17</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>24354805.04</v>
+        <v>25889478.34</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>18101537.03</v>
+        <v>19636210.33</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>12639971.51</v>
+        <v>14174644.81</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>8988656.870000005</v>
+        <v>10523330.17</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>6316700.160000004</v>
+        <v>7851373.460000001</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>3949369.280000001</v>
+        <v>5484042.579999998</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>2283865.540000007</v>
+        <v>3818538.840000004</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>891497.900000006</v>
+        <v>2426171.200000003</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0</v>
+        <v>1534673.299999997</v>
       </c>
     </row>
     <row r="4">
@@ -2010,31 +2010,31 @@
         <v>2016</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>45473898.521568</v>
+        <v>46328293.68</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>34132766.411568</v>
+        <v>34987161.57</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>25296489.581568</v>
+        <v>26150884.74</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>17812690.061568</v>
+        <v>18667085.22</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>12312781.281568</v>
+        <v>13167176.44</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>8699360.461567998</v>
+        <v>9553755.619999997</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>5538560.291568004</v>
+        <v>6392955.450000003</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>3157657.071567997</v>
+        <v>4012052.229999997</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>1210437.001567997</v>
+        <v>2064832.159999996</v>
       </c>
       <c r="K4" s="7" t="n"/>
     </row>
@@ -2043,28 +2043,28 @@
         <v>2017</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>28532703.18767959</v>
+        <v>30435655.2</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20734640.48767959</v>
+        <v>22637592.5</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>14974363.49767959</v>
+        <v>16877315.51</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>10470821.9076796</v>
+        <v>12373773.92</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>7386980.427679595</v>
+        <v>9289932.440000001</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5192201.347679593</v>
+        <v>7095153.359999999</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>3398016.987679593</v>
+        <v>5300969</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1909000.247679591</v>
+        <v>3811952.259999998</v>
       </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -2074,25 +2074,25 @@
         <v>2018</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>46200922.42690639</v>
+        <v>46400963.27</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>33677382.38690639</v>
+        <v>33877423.23</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>24396023.06690639</v>
+        <v>24596063.91</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>16491147.46690639</v>
+        <v>16691188.31</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>11893953.84690639</v>
+        <v>12093994.69</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>8469544.676906392</v>
+        <v>8669585.520000003</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>5481371.00690639</v>
+        <v>5681411.850000001</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -2103,22 +2103,22 @@
         <v>2019</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>35137405.06256086</v>
+        <v>36193254.76</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>25434199.19256086</v>
+        <v>26490048.89</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>18397726.55256086</v>
+        <v>19453576.25</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>13160613.86256086</v>
+        <v>14216463.56</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>9445948.992560856</v>
+        <v>10501798.69</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>6605892.012560859</v>
+        <v>7661741.710000001</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
@@ -2130,19 +2130,19 @@
         <v>2020</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>33116560.42906783</v>
+        <v>34107947.7</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>24417512.41906783</v>
+        <v>25408899.69</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>17321823.13906783</v>
+        <v>18313210.41</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>12111988.10906783</v>
+        <v>13103375.38</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>8717256.629067831</v>
+        <v>9708643.899999999</v>
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -2155,16 +2155,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>55549212.22331613</v>
+        <v>53044264.63</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>39395040.64331613</v>
+        <v>36890093.05</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>28351157.11331614</v>
+        <v>25846209.52</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>19303180.14331613</v>
+        <v>16798232.55</v>
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -2178,13 +2178,13 @@
         <v>2022</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>35189249.1384187</v>
+        <v>35937735.24</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>26339033.22841869</v>
+        <v>27087519.33</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>19430758.72841869</v>
+        <v>20179244.83</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
@@ -2199,10 +2199,10 @@
         <v>2023</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>35380359.06675013</v>
+        <v>35682030.93</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>26119084.33675013</v>
+        <v>26420756.2</v>
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -2218,7 +2218,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="8" t="n">
-        <v>27529870.97217109</v>
+        <v>31549381.11</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
@@ -2319,34 +2319,34 @@
         <v>2015</v>
       </c>
       <c r="B3" s="8" t="n">
-        <v>35760980.85</v>
+        <v>37295654.15</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>28121105.29</v>
+        <v>29655778.59</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>22007869.18</v>
+        <v>23542542.48</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>17206091.83</v>
+        <v>18740765.13</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>13363621.62</v>
+        <v>14898294.92</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>9988939.580000006</v>
+        <v>11523612.88</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>6781709.010000005</v>
+        <v>8316382.310000002</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>4375125.140000001</v>
+        <v>5909798.439999998</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>1872287.280000001</v>
+        <v>3406960.579999998</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0.0300000011920929</v>
+        <v>1534673.329999998</v>
       </c>
     </row>
     <row r="4">
@@ -2354,31 +2354,31 @@
         <v>2016</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>48908277.291568</v>
+        <v>49762672.45</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>38123477.881568</v>
+        <v>38977873.04</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>29670927.251568</v>
+        <v>30525322.41</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>22808194.581568</v>
+        <v>23662589.74</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>17112835.311568</v>
+        <v>17967230.47</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>12306320.931568</v>
+        <v>13160716.09</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>8155881.021568</v>
+        <v>9010276.18</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>4982630.291568004</v>
+        <v>5837025.450000003</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>1865362.501567997</v>
+        <v>2719757.659999996</v>
       </c>
       <c r="K4" s="7" t="n"/>
     </row>
@@ -2387,28 +2387,28 @@
         <v>2017</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>29629469.06767959</v>
+        <v>31532421.08</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>22970096.1576796</v>
+        <v>24873048.17</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>17359548.08767959</v>
+        <v>19262500.1</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>13279111.16767959</v>
+        <v>15182063.18</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>9721366.547679592</v>
+        <v>11624318.56</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>6696051.607679594</v>
+        <v>8599003.620000001</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4273539.447679594</v>
+        <v>6176491.460000001</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>2373669.767679594</v>
+        <v>4276621.780000001</v>
       </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -2418,25 +2418,25 @@
         <v>2018</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>48738471.05690639</v>
+        <v>48938511.9</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>38248564.61690639</v>
+        <v>38448605.46</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>29769178.45690639</v>
+        <v>29969219.3</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>23038469.40690639</v>
+        <v>23238510.25</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>17280848.78690639</v>
+        <v>17480889.63</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>12556890.11690639</v>
+        <v>12756930.96</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>8382540.61690639</v>
+        <v>8582581.460000001</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -2447,22 +2447,22 @@
         <v>2019</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>36920826.40256086</v>
+        <v>37976676.1</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>28864043.95256086</v>
+        <v>29919893.65</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>22145303.92256086</v>
+        <v>23201153.62</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>17270234.67256086</v>
+        <v>18326084.37</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>12808023.74256086</v>
+        <v>13863873.44</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>9060943.782560855</v>
+        <v>10116793.48</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
@@ -2474,19 +2474,19 @@
         <v>2020</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>34680603.12906783</v>
+        <v>35671990.4</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>27726796.23906783</v>
+        <v>28718183.51</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>21530720.70906783</v>
+        <v>22522107.98</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>16663260.03906783</v>
+        <v>17654647.31</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>12883901.06906783</v>
+        <v>13875288.34</v>
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -2499,16 +2499,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>58560632.35331614</v>
+        <v>56055684.76</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>46039806.41331614</v>
+        <v>43534858.82</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>36509267.64331613</v>
+        <v>34004320.05</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>28337972.05331614</v>
+        <v>25833024.46</v>
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -2522,13 +2522,13 @@
         <v>2022</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>37488615.7784187</v>
+        <v>38237101.88</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>29853239.1284187</v>
+        <v>30601725.23</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>23369844.04841869</v>
+        <v>24118330.15</v>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
@@ -2543,10 +2543,10 @@
         <v>2023</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>37680836.01675013</v>
+        <v>37982507.88</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>29535518.41675013</v>
+        <v>29837190.28</v>
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -2562,7 +2562,7 @@
         <v>2024</v>
       </c>
       <c r="B12" s="8" t="n">
-        <v>30198438.59217109</v>
+        <v>34217948.73</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>

--- a/demo/demo4-complete/output/post-method-triangles.xlsx
+++ b/demo/demo4-complete/output/post-method-triangles.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incurred-to-Ult" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paid-to-Ult" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reported-to-Ult" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closed-to-Ult" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average IBNR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average Unpaid" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Incurred-to-Ult" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Paid-to-Ult" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reported-to-Ult" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Closed-to-Ult" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Average IBNR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Average Unpaid" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,8 +147,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
